--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566364101</v>
+        <v>46157.93092900148</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93092900148</v>
+        <v>46157.93169510787</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93169510787</v>
+        <v>46157.93398252514</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398252514</v>
+        <v>46157.93715993055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93715993055</v>
+        <v>46158.28214605822</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214605822</v>
+        <v>46158.29676042942</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676042942</v>
+        <v>46158.29812711349</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29812711349</v>
+        <v>46158.33385591007</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33385591007</v>
+        <v>46158.36855344167</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/4. ИП Тимченко (ремонт авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855344167</v>
+        <v>46158.37286092509</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
